--- a/MavenBook/src/test/resources/RetainerInvoiceData.xlsx
+++ b/MavenBook/src/test/resources/RetainerInvoiceData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Customer Name</t>
   </si>
@@ -56,13 +56,7 @@
     <t>SAVE AND APPROVE</t>
   </si>
   <si>
-    <t>27-12-2025</t>
-  </si>
-  <si>
     <t>subinm</t>
-  </si>
-  <si>
-    <t>27-12-2026</t>
   </si>
   <si>
     <t>Terms 1: Test 101</t>
@@ -533,9 +527,7 @@
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="B2" s="5"/>
       <c r="C2" s="4">
         <v>1001</v>
       </c>
@@ -557,11 +549,9 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B3" s="5"/>
       <c r="C3" s="4">
         <v>1002</v>
       </c>
@@ -572,13 +562,13 @@
         <v>101</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">

--- a/MavenBook/src/test/resources/RetainerInvoiceData.xlsx
+++ b/MavenBook/src/test/resources/RetainerInvoiceData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Customer Name</t>
   </si>
@@ -38,9 +38,6 @@
     <t>Terms And Conditions</t>
   </si>
   <si>
-    <t>Rency</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -56,9 +53,6 @@
     <t>SAVE AND APPROVE</t>
   </si>
   <si>
-    <t>subinm</t>
-  </si>
-  <si>
     <t>Terms 1: Test 101</t>
   </si>
   <si>
@@ -66,6 +60,9 @@
   </si>
   <si>
     <t>SAVE AND SUBMIT</t>
+  </si>
+  <si>
+    <t>Deepak T</t>
   </si>
 </sst>
 </file>
@@ -515,7 +512,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="10"/>
@@ -525,50 +522,50 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="4">
         <v>1001</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2">
         <v>100</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="H2" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="4">
         <v>1002</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2">
         <v>101</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>14</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
